--- a/HanLexicon.Api/New folder/testImportV.xlsx
+++ b/HanLexicon.Api/New folder/testImportV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\HanLexicon\HanLexicon.Api\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B8BB80-AFE6-4CF4-B1A5-1C9F4B429F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F3464B-8CB6-4339-B29A-6A4A6CE23BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="84">
   <si>
     <t>Từ vựng</t>
   </si>
@@ -66,12 +66,6 @@
     <t>Xin chào</t>
   </si>
   <si>
-    <t>https://img.com/nihao.png</t>
-  </si>
-  <si>
-    <t>https://audio.com/nihao.mp3</t>
-  </si>
-  <si>
     <t>Hello</t>
   </si>
   <si>
@@ -93,12 +87,6 @@
     <t>Cảm ơn</t>
   </si>
   <si>
-    <t>https://img.com/xiexie.png</t>
-  </si>
-  <si>
-    <t>https://audio.com/xiexie.mp3</t>
-  </si>
-  <si>
     <t>Thank you</t>
   </si>
   <si>
@@ -117,12 +105,6 @@
     <t>Tạm biệt</t>
   </si>
   <si>
-    <t>https://img.com/zaijian.png</t>
-  </si>
-  <si>
-    <t>https://audio.com/zaijian.mp3</t>
-  </si>
-  <si>
     <t>Goodbye</t>
   </si>
   <si>
@@ -144,12 +126,6 @@
     <t>Quả táo</t>
   </si>
   <si>
-    <t>https://img.com/apple.png</t>
-  </si>
-  <si>
-    <t>https://audio.com/apple.mp3</t>
-  </si>
-  <si>
     <t>Apple</t>
   </si>
   <si>
@@ -171,12 +147,6 @@
     <t>Thích</t>
   </si>
   <si>
-    <t>https://img.com/like.png</t>
-  </si>
-  <si>
-    <t>https://audio.com/like.mp3</t>
-  </si>
-  <si>
     <t>Like</t>
   </si>
   <si>
@@ -198,12 +168,6 @@
     <t>Học tập</t>
   </si>
   <si>
-    <t>https://img.com/study.png</t>
-  </si>
-  <si>
-    <t>https://audio.com/study.mp3</t>
-  </si>
-  <si>
     <t>Study / Learn</t>
   </si>
   <si>
@@ -225,12 +189,6 @@
     <t>Bạn bè</t>
   </si>
   <si>
-    <t>https://img.com/friend.png</t>
-  </si>
-  <si>
-    <t>https://audio.com/friend.mp3</t>
-  </si>
-  <si>
     <t>Friend</t>
   </si>
   <si>
@@ -252,12 +210,6 @@
     <t>Công việc / Làm việc</t>
   </si>
   <si>
-    <t>https://img.com/work.png</t>
-  </si>
-  <si>
-    <t>https://audio.com/work.mp3</t>
-  </si>
-  <si>
     <t>Work</t>
   </si>
   <si>
@@ -279,12 +231,6 @@
     <t>Bệnh viện</t>
   </si>
   <si>
-    <t>https://img.com/hospital.png</t>
-  </si>
-  <si>
-    <t>https://audio.com/hospital.mp3</t>
-  </si>
-  <si>
     <t>Hospital</t>
   </si>
   <si>
@@ -306,12 +252,6 @@
     <t>Xinh đẹp</t>
   </si>
   <si>
-    <t>https://img.com/pretty.png</t>
-  </si>
-  <si>
-    <t>https://audio.com/pretty.mp3</t>
-  </si>
-  <si>
     <t>Beautiful / Pretty</t>
   </si>
   <si>
@@ -331,13 +271,19 @@
   </si>
   <si>
     <t>29fa1a00-8be7-48sed-8f22-b3950fd0ed34</t>
+  </si>
+  <si>
+    <t>https://interactive-examples.mdn.mozilla.net/media/cc0-audio/t-rex-roar.mp3</t>
+  </si>
+  <si>
+    <t>https://fastly.picsum.photos/id/1039/400/400.jpg?hmac=eGTJv6h3WS1O4ocu4ucKkZ35a_YiLCKQycE0NSy1yaE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,6 +313,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -410,10 +364,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -422,8 +377,14 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -709,7 +670,7 @@
     <col min="2" max="2" width="14.26953125" customWidth="1"/>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
     <col min="4" max="4" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="5" max="5" width="23" style="6" customWidth="1"/>
     <col min="6" max="6" width="24.81640625" customWidth="1"/>
     <col min="7" max="7" width="16.26953125" customWidth="1"/>
     <col min="8" max="8" width="21.6328125" customWidth="1"/>
@@ -730,7 +691,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -749,7 +710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="28">
+    <row r="2" spans="1:10" ht="87.5">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -760,315 +721,329 @@
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="87.5">
+      <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" ht="28">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G3" s="1" t="s">
+    <row r="4" spans="1:10" ht="87.5">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" ht="28">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="2" t="s">
+    <row r="5" spans="1:10" ht="87.5">
+      <c r="A5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="D5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="J5" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" ht="28">
-      <c r="A5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="6" spans="1:10" ht="87.5">
+      <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="1" t="s">
+    </row>
+    <row r="7" spans="1:10" ht="87.5">
+      <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="B7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" ht="28">
-      <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="1" t="s">
+    <row r="8" spans="1:10" ht="87.5">
+      <c r="A8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="D8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" ht="28">
-      <c r="A7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="2" t="s">
+    <row r="9" spans="1:10" ht="87.5">
+      <c r="A9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="D9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="I9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="8" spans="1:10" ht="28">
-      <c r="A8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="1" t="s">
+    <row r="10" spans="1:10" ht="87.5">
+      <c r="A10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="D10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28">
-      <c r="A9" s="1" t="s">
+    <row r="11" spans="1:10" ht="87.5">
+      <c r="A11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="H11" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="28">
-      <c r="A10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="28">
-      <c r="A11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{F5C16694-97DE-414F-9C73-53127BB97F2F}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{50D089A8-4993-4681-A897-1F0616EBD7EA}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{BF729FC4-4AAB-4DF0-8CCF-DC0ED33B64B3}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{A2D9FDA1-DEFC-4BB8-9765-80AB611A80C4}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{8A69AABE-03D2-4093-886C-64C43AC1B499}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{84EBED28-E0C5-4E93-B376-BF3C31281E08}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{774F1648-2AD7-4CD9-905A-AA4D97560BA6}"/>
+    <hyperlink ref="E9" r:id="rId8" xr:uid="{96D10286-73D7-4442-B5DC-5ECCC4B501DF}"/>
+    <hyperlink ref="E10" r:id="rId9" xr:uid="{F615C0A8-6583-470F-AFAD-5ABB1C512553}"/>
+    <hyperlink ref="E11" r:id="rId10" xr:uid="{5E7455AB-BF03-4148-9708-3F7BD8D4D134}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/HanLexicon.Api/New folder/testImportV.xlsx
+++ b/HanLexicon.Api/New folder/testImportV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\HanLexicon\HanLexicon.Api\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F3464B-8CB6-4339-B29A-6A4A6CE23BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A56BEEA-9E5F-4088-8188-4EC715113BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
   <si>
     <t>Từ vựng</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Link ảnh</t>
   </si>
   <si>
-    <t>Mã bài học</t>
-  </si>
-  <si>
     <t>Link âm thanh</t>
   </si>
   <si>
@@ -262,15 +259,6 @@
   </si>
   <si>
     <t>Bộ quần áo này rất đẹp.</t>
-  </si>
-  <si>
-    <t>29fa1a00-8be7-48ed-8f22-b3950fd0ed34</t>
-  </si>
-  <si>
-    <t>29fa1a00-8be7-48ed-8f22-b3950fd0ed41</t>
-  </si>
-  <si>
-    <t>29fa1a00-8be7-48sed-8f22-b3950fd0ed34</t>
   </si>
   <si>
     <t>https://interactive-examples.mdn.mozilla.net/media/cc0-audio/t-rex-roar.mp3</t>
@@ -663,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.453125" customWidth="1"/>
@@ -671,14 +659,13 @@
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
     <col min="4" max="4" width="15.1796875" customWidth="1"/>
     <col min="5" max="5" width="23" style="6" customWidth="1"/>
-    <col min="6" max="6" width="24.81640625" customWidth="1"/>
-    <col min="7" max="7" width="16.26953125" customWidth="1"/>
-    <col min="8" max="8" width="21.6328125" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" customWidth="1"/>
-    <col min="10" max="10" width="18.7265625" customWidth="1"/>
+    <col min="6" max="6" width="16.26953125" customWidth="1"/>
+    <col min="7" max="7" width="21.6328125" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -692,42 +679,39 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="87.5">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="87.5">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>13</v>
@@ -738,28 +722,25 @@
       <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="87.5">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="87.5">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
@@ -770,28 +751,25 @@
       <c r="I3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="87.5">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="87.5">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>26</v>
@@ -802,28 +780,25 @@
       <c r="I4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="87.5">
+      <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="87.5">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>33</v>
@@ -834,28 +809,25 @@
       <c r="I5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:9" ht="87.5">
+      <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="87.5">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>40</v>
@@ -866,28 +838,25 @@
       <c r="I6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:9" ht="87.5">
+      <c r="A7" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="87.5">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>47</v>
@@ -898,28 +867,25 @@
       <c r="I7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:9" ht="87.5">
+      <c r="A8" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="87.5">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>54</v>
@@ -930,28 +896,25 @@
       <c r="I8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:9" ht="87.5">
+      <c r="A9" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="87.5">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>61</v>
@@ -962,28 +925,25 @@
       <c r="I9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="87.5">
+      <c r="A10" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="87.5">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>68</v>
@@ -994,28 +954,25 @@
       <c r="I10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="J10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:9" ht="87.5">
+      <c r="A11" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="87.5">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>75</v>
@@ -1025,9 +982,6 @@
       </c>
       <c r="I11" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
